--- a/data/synthetic/partner_schedule.xlsx
+++ b/data/synthetic/partner_schedule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Milestones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-23T08:15:00Z</t>
+          <t>2026-09-11T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-01T09:00:00Z</t>
+          <t>2026-07-31T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-20T10:00:00Z</t>
+          <t>2026-09-08T17:16:20.452995Z</t>
         </is>
       </c>
     </row>
